--- a/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0003T0006Z000C1N7_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0003T0006Z000C1N7_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>44.98838978469335</v>
+        <v>7.310613340012669</v>
       </c>
       <c r="D2" t="n">
-        <v>44.85164158742039</v>
+        <v>7.288391757955814</v>
       </c>
       <c r="E2" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F2" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>98.10460709223926</v>
+        <v>15.94199865248888</v>
       </c>
       <c r="D3" t="n">
-        <v>98.27946786284157</v>
+        <v>15.97041352771176</v>
       </c>
       <c r="E3" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F3" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.78464874647569</v>
+        <v>4.027505421302299</v>
       </c>
       <c r="D4" t="n">
-        <v>24.13939275064781</v>
+        <v>3.92265132198027</v>
       </c>
       <c r="E4" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F4" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>82.31001969628988</v>
+        <v>13.37537820064711</v>
       </c>
       <c r="D5" t="n">
-        <v>82.54764804360487</v>
+        <v>13.41399280708579</v>
       </c>
       <c r="E5" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F5" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>108.4522485571186</v>
+        <v>17.62349039053176</v>
       </c>
       <c r="D6" t="n">
-        <v>108.551481044038</v>
+        <v>17.63961566965618</v>
       </c>
       <c r="E6" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F6" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>89.9089092100333</v>
+        <v>14.61019774663041</v>
       </c>
       <c r="D7" t="n">
-        <v>90.06714869035255</v>
+        <v>14.63591166218229</v>
       </c>
       <c r="E7" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F7" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>120.3409639441149</v>
+        <v>19.55540664091868</v>
       </c>
       <c r="D8" t="n">
-        <v>120.3781185086114</v>
+        <v>19.56144425764936</v>
       </c>
       <c r="E8" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F8" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>94.44943550789293</v>
+        <v>15.3480332700326</v>
       </c>
       <c r="D9" t="n">
-        <v>94.57241011552377</v>
+        <v>15.36801664377261</v>
       </c>
       <c r="E9" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F9" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>81.86276782057024</v>
+        <v>13.30269977084266</v>
       </c>
       <c r="D10" t="n">
-        <v>82.01897958607209</v>
+        <v>13.32808418273672</v>
       </c>
       <c r="E10" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F10" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>33.47411652019641</v>
+        <v>5.439543934531917</v>
       </c>
       <c r="D11" t="n">
-        <v>34.12470309378458</v>
+        <v>5.545264252739995</v>
       </c>
       <c r="E11" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F11" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>91.6430351973555</v>
+        <v>14.89199321957027</v>
       </c>
       <c r="D12" t="n">
-        <v>91.6956642494843</v>
+        <v>14.9005454405412</v>
       </c>
       <c r="E12" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F12" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>22.28848514818994</v>
+        <v>3.621878836580866</v>
       </c>
       <c r="D13" t="n">
-        <v>23.48502294385075</v>
+        <v>3.816316228375748</v>
       </c>
       <c r="E13" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F13" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>79.20935392877895</v>
+        <v>12.87152001342658</v>
       </c>
       <c r="D14" t="n">
-        <v>79.30402794418826</v>
+        <v>12.88690454093059</v>
       </c>
       <c r="E14" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F14" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>12.35900068610661</v>
+        <v>2.008337611492325</v>
       </c>
       <c r="D15" t="n">
-        <v>14.0017635573541</v>
+        <v>2.275286578070042</v>
       </c>
       <c r="E15" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F15" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>60.50200318836804</v>
+        <v>9.831575518109807</v>
       </c>
       <c r="D16" t="n">
-        <v>60.75744971543399</v>
+        <v>9.873085578758024</v>
       </c>
       <c r="E16" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F16" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>65.34082367473441</v>
+        <v>10.61788384714434</v>
       </c>
       <c r="D17" t="n">
-        <v>65.50599485139277</v>
+        <v>10.64472416335133</v>
       </c>
       <c r="E17" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F17" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>48.6147826207685</v>
+        <v>7.899902175874882</v>
       </c>
       <c r="D18" t="n">
-        <v>49.57640574939617</v>
+        <v>8.056165934276878</v>
       </c>
       <c r="E18" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F18" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>49.18693954538332</v>
+        <v>7.992877676124791</v>
       </c>
       <c r="D19" t="n">
-        <v>49.44163260304471</v>
+        <v>8.034265297994766</v>
       </c>
       <c r="E19" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F19" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>68.63803189130104</v>
+        <v>11.15368018233642</v>
       </c>
       <c r="D20" t="n">
-        <v>68.70350676858153</v>
+        <v>11.1643198498945</v>
       </c>
       <c r="E20" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F20" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>61.84662791003817</v>
+        <v>10.0500770353812</v>
       </c>
       <c r="D21" t="n">
-        <v>61.92979995051433</v>
+        <v>10.06359249195858</v>
       </c>
       <c r="E21" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F21" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>103.7202470375711</v>
+        <v>16.85454014360531</v>
       </c>
       <c r="D22" t="n">
-        <v>103.6623141046876</v>
+        <v>16.84512604201173</v>
       </c>
       <c r="E22" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F22" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>48.8637409067286</v>
+        <v>7.940357897343398</v>
       </c>
       <c r="D23" t="n">
-        <v>49.01404539668814</v>
+        <v>7.964782376961823</v>
       </c>
       <c r="E23" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F23" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>39.65949642211007</v>
+        <v>6.444668168592886</v>
       </c>
       <c r="D24" t="n">
-        <v>39.92647035248326</v>
+        <v>6.48805143227853</v>
       </c>
       <c r="E24" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F24" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>91.01683547817358</v>
+        <v>14.79023576520321</v>
       </c>
       <c r="D25" t="n">
-        <v>90.94163059695961</v>
+        <v>14.77801497200594</v>
       </c>
       <c r="E25" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F25" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>65.55357144547598</v>
+        <v>10.65245535988985</v>
       </c>
       <c r="D26" t="n">
-        <v>65.53767856024626</v>
+        <v>10.64987276604002</v>
       </c>
       <c r="E26" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F26" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>36.54184902684478</v>
+        <v>5.938050466862277</v>
       </c>
       <c r="D27" t="n">
-        <v>36.91910650772782</v>
+        <v>5.999354807505771</v>
       </c>
       <c r="E27" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F27" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>39.16047402146842</v>
+        <v>6.363577028488618</v>
       </c>
       <c r="D28" t="n">
-        <v>40.84061719234627</v>
+        <v>6.636600293756269</v>
       </c>
       <c r="E28" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F28" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>28.59701416769211</v>
+        <v>4.647014802249968</v>
       </c>
       <c r="D29" t="n">
-        <v>28.8443104199057</v>
+        <v>4.687200443234676</v>
       </c>
       <c r="E29" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F29" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>43.53579485519324</v>
+        <v>7.074566663968901</v>
       </c>
       <c r="D30" t="n">
-        <v>45.19968128506666</v>
+        <v>7.344948208823332</v>
       </c>
       <c r="E30" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F30" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>41.02737459433627</v>
+        <v>6.666948371579643</v>
       </c>
       <c r="D31" t="n">
-        <v>41.07019651661879</v>
+        <v>6.673906933950554</v>
       </c>
       <c r="E31" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F31" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>85.45192472492302</v>
+        <v>13.88593776779999</v>
       </c>
       <c r="D32" t="n">
-        <v>85.33984872383226</v>
+        <v>13.86772541762274</v>
       </c>
       <c r="E32" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F32" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>93.66030387983466</v>
+        <v>15.21979938047313</v>
       </c>
       <c r="D33" t="n">
-        <v>93.53905748714752</v>
+        <v>15.20009684166147</v>
       </c>
       <c r="E33" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F33" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>20.46052127856204</v>
+        <v>3.324834707766332</v>
       </c>
       <c r="D34" t="n">
-        <v>20.67654082351463</v>
+        <v>3.359937883821128</v>
       </c>
       <c r="E34" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F34" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>19.57157595076448</v>
+        <v>3.180381091999229</v>
       </c>
       <c r="D35" t="n">
-        <v>19.89439935235164</v>
+        <v>3.232839894757142</v>
       </c>
       <c r="E35" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F35" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>31.17692153018611</v>
+        <v>5.066249748655244</v>
       </c>
       <c r="D36" t="n">
-        <v>31.17439634304093</v>
+        <v>5.065839405744151</v>
       </c>
       <c r="E36" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F36" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>37.9645594190817</v>
+        <v>6.169240905600776</v>
       </c>
       <c r="D37" t="n">
-        <v>38.27136823114036</v>
+        <v>6.219097337560308</v>
       </c>
       <c r="E37" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F37" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1632,16 +1632,16 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>58.87147474369954</v>
+        <v>9.566614645851175</v>
       </c>
       <c r="D38" t="n">
-        <v>58.76373047833974</v>
+        <v>9.549106202730208</v>
       </c>
       <c r="E38" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F38" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1664,16 +1664,16 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>89.11450918347683</v>
+        <v>14.48110774231498</v>
       </c>
       <c r="D39" t="n">
-        <v>88.93694522305606</v>
+        <v>14.45225359874661</v>
       </c>
       <c r="E39" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F39" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1696,16 +1696,16 @@
         <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>16.47449600552115</v>
+        <v>2.677105600897186</v>
       </c>
       <c r="D40" t="n">
-        <v>16.84722649600963</v>
+        <v>2.737674305601565</v>
       </c>
       <c r="E40" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F40" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1728,16 +1728,16 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>83.84040697211069</v>
+        <v>13.62406613296799</v>
       </c>
       <c r="D41" t="n">
-        <v>83.64860154360967</v>
+        <v>13.59289775083657</v>
       </c>
       <c r="E41" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F41" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1760,16 +1760,16 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>43.40370148862845</v>
+        <v>7.053101491902123</v>
       </c>
       <c r="D42" t="n">
-        <v>43.56684910534456</v>
+        <v>7.079612979618491</v>
       </c>
       <c r="E42" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F42" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1792,16 +1792,16 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>34.42153288483909</v>
+        <v>5.593499093786352</v>
       </c>
       <c r="D43" t="n">
-        <v>34.60097779616843</v>
+        <v>5.62265889187737</v>
       </c>
       <c r="E43" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F43" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>12.98518288169136</v>
+        <v>2.110092218274846</v>
       </c>
       <c r="D44" t="n">
-        <v>13.07128512598468</v>
+        <v>2.124083832972511</v>
       </c>
       <c r="E44" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F44" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1856,16 +1856,16 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>29.31610064744925</v>
+        <v>4.763866355210503</v>
       </c>
       <c r="D45" t="n">
-        <v>29.39362810262052</v>
+        <v>4.776464566675835</v>
       </c>
       <c r="E45" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F45" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1888,16 +1888,16 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>35.24735194062271</v>
+        <v>5.727694690351191</v>
       </c>
       <c r="D46" t="n">
-        <v>35.03041884000641</v>
+        <v>5.692443061501042</v>
       </c>
       <c r="E46" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F46" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1920,16 +1920,16 @@
         <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>30.53204901976557</v>
+        <v>4.961457965711905</v>
       </c>
       <c r="D47" t="n">
-        <v>30.2067911959298</v>
+        <v>4.908603569338593</v>
       </c>
       <c r="E47" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F47" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1952,16 +1952,16 @@
         <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>16.66175104531778</v>
+        <v>2.70753454486414</v>
       </c>
       <c r="D48" t="n">
-        <v>16.47457496966194</v>
+        <v>2.677118432570066</v>
       </c>
       <c r="E48" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F48" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1984,16 +1984,16 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>57.57651284296305</v>
+        <v>9.356183336981495</v>
       </c>
       <c r="D49" t="n">
-        <v>57.30757400882636</v>
+        <v>9.312480776434285</v>
       </c>
       <c r="E49" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F49" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2016,16 +2016,16 @@
         <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>45.41831758366196</v>
+        <v>7.380476607345068</v>
       </c>
       <c r="D50" t="n">
-        <v>45.19711350947779</v>
+        <v>7.344530945290142</v>
       </c>
       <c r="E50" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F50" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2048,16 +2048,16 @@
         <v>50</v>
       </c>
       <c r="C51" t="n">
-        <v>24.77644686171021</v>
+        <v>4.026172615027909</v>
       </c>
       <c r="D51" t="n">
-        <v>24.70269066586904</v>
+        <v>4.014187233203719</v>
       </c>
       <c r="E51" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F51" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2080,16 +2080,16 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>27.25017948056949</v>
+        <v>4.428154165592542</v>
       </c>
       <c r="D52" t="n">
-        <v>26.86930133385672</v>
+        <v>4.366261466751718</v>
       </c>
       <c r="E52" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F52" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2112,16 +2112,16 @@
         <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>42.40306167964485</v>
+        <v>6.890497522942288</v>
       </c>
       <c r="D53" t="n">
-        <v>42.23221645548985</v>
+        <v>6.862735174017102</v>
       </c>
       <c r="E53" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F53" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2144,16 +2144,16 @@
         <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>28.71552432291959</v>
+        <v>4.666272702474433</v>
       </c>
       <c r="D54" t="n">
-        <v>28.39821537768183</v>
+        <v>4.614709998873298</v>
       </c>
       <c r="E54" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F54" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2176,16 +2176,16 @@
         <v>54</v>
       </c>
       <c r="C55" t="n">
-        <v>94.90648138235838</v>
+        <v>15.42230322463324</v>
       </c>
       <c r="D55" t="n">
-        <v>94.6031467262562</v>
+        <v>15.37301134301663</v>
       </c>
       <c r="E55" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F55" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2208,16 +2208,16 @@
         <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>39.43815924894843</v>
+        <v>6.408700877954121</v>
       </c>
       <c r="D56" t="n">
-        <v>39.3099954286175</v>
+        <v>6.387874257150345</v>
       </c>
       <c r="E56" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F56" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2240,16 +2240,16 @@
         <v>56</v>
       </c>
       <c r="C57" t="n">
-        <v>35.73841703238602</v>
+        <v>5.807492767762728</v>
       </c>
       <c r="D57" t="n">
-        <v>35.4715445003042</v>
+        <v>5.764125981299434</v>
       </c>
       <c r="E57" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F57" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2272,16 +2272,16 @@
         <v>57</v>
       </c>
       <c r="C58" t="n">
-        <v>47.75192614522939</v>
+        <v>7.759687998599776</v>
       </c>
       <c r="D58" t="n">
-        <v>47.37674561648441</v>
+        <v>7.698721162678717</v>
       </c>
       <c r="E58" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F58" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2304,16 +2304,16 @@
         <v>58</v>
       </c>
       <c r="C59" t="n">
-        <v>39.99744653719502</v>
+        <v>6.499585062294191</v>
       </c>
       <c r="D59" t="n">
-        <v>39.69719008974274</v>
+        <v>6.450793389583196</v>
       </c>
       <c r="E59" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F59" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2336,16 +2336,16 @@
         <v>59</v>
       </c>
       <c r="C60" t="n">
-        <v>78.08169124954392</v>
+        <v>12.68827482805089</v>
       </c>
       <c r="D60" t="n">
-        <v>77.73598505719741</v>
+        <v>12.63209757179458</v>
       </c>
       <c r="E60" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F60" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2368,16 +2368,16 @@
         <v>60</v>
       </c>
       <c r="C61" t="n">
-        <v>38.28938647137562</v>
+        <v>6.222025301598539</v>
       </c>
       <c r="D61" t="n">
-        <v>37.90387645512884</v>
+        <v>6.159379923958436</v>
       </c>
       <c r="E61" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F61" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2400,16 +2400,16 @@
         <v>61</v>
       </c>
       <c r="C62" t="n">
-        <v>94.6990848122468</v>
+        <v>15.38860128199011</v>
       </c>
       <c r="D62" t="n">
-        <v>94.36934933705714</v>
+        <v>15.33501926727179</v>
       </c>
       <c r="E62" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F62" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2432,16 +2432,16 @@
         <v>62</v>
       </c>
       <c r="C63" t="n">
-        <v>55.7353368869399</v>
+        <v>9.056992244127734</v>
       </c>
       <c r="D63" t="n">
-        <v>55.35267325683661</v>
+        <v>8.99480940423595</v>
       </c>
       <c r="E63" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F63" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2464,16 +2464,16 @@
         <v>63</v>
       </c>
       <c r="C64" t="n">
-        <v>103.9406691047247</v>
+        <v>16.89035872951777</v>
       </c>
       <c r="D64" t="n">
-        <v>103.6164598065879</v>
+        <v>16.83767471857054</v>
       </c>
       <c r="E64" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F64" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2496,16 +2496,16 @@
         <v>64</v>
       </c>
       <c r="C65" t="n">
-        <v>86.6074908660304</v>
+        <v>14.07371726572994</v>
       </c>
       <c r="D65" t="n">
-        <v>86.26286157772584</v>
+        <v>14.01771500638045</v>
       </c>
       <c r="E65" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F65" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2528,16 +2528,16 @@
         <v>65</v>
       </c>
       <c r="C66" t="n">
-        <v>20.13365832457838</v>
+        <v>3.271719477743987</v>
       </c>
       <c r="D66" t="n">
-        <v>20.01205192433355</v>
+        <v>3.251958437704201</v>
       </c>
       <c r="E66" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F66" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2560,16 +2560,16 @@
         <v>66</v>
       </c>
       <c r="C67" t="n">
-        <v>44.31287680210327</v>
+        <v>7.200842480341781</v>
       </c>
       <c r="D67" t="n">
-        <v>43.97692390999261</v>
+        <v>7.1462501353738</v>
       </c>
       <c r="E67" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F67" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2592,16 +2592,16 @@
         <v>67</v>
       </c>
       <c r="C68" t="n">
-        <v>41.3875371988167</v>
+        <v>6.725474794807714</v>
       </c>
       <c r="D68" t="n">
-        <v>41.53410449854776</v>
+        <v>6.749291981014011</v>
       </c>
       <c r="E68" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F68" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2624,16 +2624,16 @@
         <v>68</v>
       </c>
       <c r="C69" t="n">
-        <v>81.65425065286117</v>
+        <v>13.26881573108994</v>
       </c>
       <c r="D69" t="n">
-        <v>81.29035339414023</v>
+        <v>13.20968242654779</v>
       </c>
       <c r="E69" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F69" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2656,16 +2656,16 @@
         <v>69</v>
       </c>
       <c r="C70" t="n">
-        <v>58.20054436818642</v>
+        <v>9.457588459830294</v>
       </c>
       <c r="D70" t="n">
-        <v>57.81392659148212</v>
+        <v>9.394763071115843</v>
       </c>
       <c r="E70" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F70" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2688,16 +2688,16 @@
         <v>70</v>
       </c>
       <c r="C71" t="n">
-        <v>52.84000962875802</v>
+        <v>8.586501564673178</v>
       </c>
       <c r="D71" t="n">
-        <v>52.50481335562412</v>
+        <v>8.53203217028892</v>
       </c>
       <c r="E71" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F71" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2720,16 +2720,16 @@
         <v>71</v>
       </c>
       <c r="C72" t="n">
-        <v>68.36696326072641</v>
+        <v>11.10963152986804</v>
       </c>
       <c r="D72" t="n">
-        <v>67.99332273790351</v>
+        <v>11.04891494490932</v>
       </c>
       <c r="E72" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F72" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -2752,16 +2752,16 @@
         <v>72</v>
       </c>
       <c r="C73" t="n">
-        <v>46.83069717109563</v>
+        <v>7.60998829030304</v>
       </c>
       <c r="D73" t="n">
-        <v>47.06979451363214</v>
+        <v>7.648841608465223</v>
       </c>
       <c r="E73" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F73" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -2784,16 +2784,16 @@
         <v>73</v>
       </c>
       <c r="C74" t="n">
-        <v>92.72885238799083</v>
+        <v>15.06843851304851</v>
       </c>
       <c r="D74" t="n">
-        <v>92.36318807547704</v>
+        <v>15.00901806226502</v>
       </c>
       <c r="E74" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F74" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -2816,16 +2816,16 @@
         <v>74</v>
       </c>
       <c r="C75" t="n">
-        <v>34.24102117145745</v>
+        <v>5.564165940361836</v>
       </c>
       <c r="D75" t="n">
-        <v>34.48041311946375</v>
+        <v>5.60306713191286</v>
       </c>
       <c r="E75" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F75" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -2848,16 +2848,16 @@
         <v>75</v>
       </c>
       <c r="C76" t="n">
-        <v>23.60814756654414</v>
+        <v>3.836323979563423</v>
       </c>
       <c r="D76" t="n">
-        <v>23.79874500182941</v>
+        <v>3.86729606279728</v>
       </c>
       <c r="E76" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F76" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -2880,16 +2880,16 @@
         <v>76</v>
       </c>
       <c r="C77" t="n">
-        <v>60.16935154712934</v>
+        <v>9.777519626408518</v>
       </c>
       <c r="D77" t="n">
-        <v>59.80791328836174</v>
+        <v>9.718785909358783</v>
       </c>
       <c r="E77" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F77" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -2912,16 +2912,16 @@
         <v>77</v>
       </c>
       <c r="C78" t="n">
-        <v>64.44397309640497</v>
+        <v>10.47214562816581</v>
       </c>
       <c r="D78" t="n">
-        <v>64.06382802103202</v>
+        <v>10.4103720534177</v>
       </c>
       <c r="E78" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F78" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -2944,16 +2944,16 @@
         <v>78</v>
       </c>
       <c r="C79" t="n">
-        <v>2.52470927497578</v>
+        <v>0.4102652571835643</v>
       </c>
       <c r="D79" t="n">
-        <v>2.37371705584419</v>
+        <v>0.3857290215746809</v>
       </c>
       <c r="E79" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F79" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -2976,16 +2976,16 @@
         <v>79</v>
       </c>
       <c r="C80" t="n">
-        <v>12.38484093883098</v>
+        <v>2.012536652560034</v>
       </c>
       <c r="D80" t="n">
-        <v>12.65041452360991</v>
+        <v>2.05569236008661</v>
       </c>
       <c r="E80" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F80" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3008,16 +3008,16 @@
         <v>80</v>
       </c>
       <c r="C81" t="n">
-        <v>50.00604901681001</v>
+        <v>8.125982965231627</v>
       </c>
       <c r="D81" t="n">
-        <v>50.27661263229431</v>
+        <v>8.169949552747825</v>
       </c>
       <c r="E81" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F81" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3040,16 +3040,16 @@
         <v>81</v>
       </c>
       <c r="C82" t="n">
-        <v>70.71783844084597</v>
+        <v>11.49164874663747</v>
       </c>
       <c r="D82" t="n">
-        <v>70.33280376120773</v>
+        <v>11.42908061119626</v>
       </c>
       <c r="E82" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F82" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3072,16 +3072,16 @@
         <v>82</v>
       </c>
       <c r="C83" t="n">
-        <v>91.11993031053129</v>
+        <v>14.80698867546134</v>
       </c>
       <c r="D83" t="n">
-        <v>90.74391050271647</v>
+        <v>14.74588545669143</v>
       </c>
       <c r="E83" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F83" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3104,16 +3104,16 @@
         <v>83</v>
       </c>
       <c r="C84" t="n">
-        <v>107.2597436711007</v>
+        <v>17.42970834655387</v>
       </c>
       <c r="D84" t="n">
-        <v>106.8994097800171</v>
+        <v>17.37115408925278</v>
       </c>
       <c r="E84" t="n">
-        <v>28.09498506990656</v>
+        <v>4.565435073859816</v>
       </c>
       <c r="F84" t="n">
-        <v>27.97579355954269</v>
+        <v>4.546066453425687</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
